--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/createAdmin-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/createAdmin-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="55">
   <si>
     <t>Statement: createAdmin(data: CreateAdminInput): Promise&lt;ActionResult&lt;AdminWithUser&gt;&gt; — validates input with Zod, delegates to userService.createAdmin(), and returns the persisted admin wrapped in ActionResult.</t>
   </si>
@@ -122,6 +122,19 @@
   </si>
   <si>
     <t>No change</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin "admin@gym.test" seeded via userService.createAdmin() (TC2 conflict scenario already resolved).
+const input: CreateAdminInput = { email: "admin2@gym.test", fullName: "Admin Two", phone: "+40700000011", dateOfBirth: "1987-04-15", password: "AdminPass123!" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { id: defined, user: { email: "admin2@gym.test", role: "ADMIN" } } }</t>
+  </si>
+  <si>
+    <t>Two admin rows present; first admin row unchanged</t>
   </si>
   <si>
     <t>Testing</t>
@@ -806,7 +819,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -906,6 +919,29 @@
         <v>34</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -934,17 +970,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -956,40 +992,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -997,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
